--- a/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/Cubes/CubeFromRange-Output.xlsx
@@ -696,55 +696,69 @@
       <x:c r="A3" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B3" s="0" vm="4">
+      <x:c r="B3" s="0" t="str" vm="4">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Measures].[Sum of Price]")</x:f>
-      </x:c>
-      <x:c r="C3" s="0" vm="6">
+        <x:v>Sum of Price</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="str" vm="6">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Measures].[Sum of Amount]")</x:f>
+        <x:v>Sum of Amount</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A4" s="1" vm="5">
+      <x:c r="A4" s="1" t="str" vm="5">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].&amp;[Baclava]")</x:f>
+        <x:v>Baclava</x:v>
       </x:c>
       <x:c r="B4" s="0" vm="13">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A4,B$3)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="0" vm="14">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A4,C$3)</x:f>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A5" s="1" vm="3">
+      <x:c r="A5" s="1" t="str" vm="3">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].&amp;[Cake]")</x:f>
+        <x:v>Cake</x:v>
       </x:c>
       <x:c r="B5" s="0" vm="11">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A5,B$3)</x:f>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="0" vm="12">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A5,C$3)</x:f>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A6" s="1" vm="2">
+      <x:c r="A6" s="1" t="str" vm="2">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].&amp;[Pie]")</x:f>
+        <x:v>Pie</x:v>
       </x:c>
       <x:c r="B6" s="0" vm="9">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A6,B$3)</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="0" vm="10">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A6,C$3)</x:f>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A7" s="1" vm="1">
+      <x:c r="A7" s="1" t="str" vm="1">
         <x:f>CUBEMEMBER("ThisWorkbookDataModel","[Range].[Pastry].[All]","Grand Total")</x:f>
+        <x:v>Grand Total</x:v>
       </x:c>
       <x:c r="B7" s="0" vm="7">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A7,B$3)</x:f>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C7" s="0" vm="8">
         <x:f>CUBEVALUE("ThisWorkbookDataModel",$A7,C$3)</x:f>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
